--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7BA33D-A4FB-44D2-9241-789D91B7D5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA16F3D-8739-4637-8B88-7FCBD75E0057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
-    <sheet name="맵(100~199)" sheetId="3" r:id="rId1"/>
+    <sheet name="맵&amp;포탈(000~999)" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -24,17 +24,81 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>윤형석</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{42876F14-2832-45A8-A79E-E6E9B94D7108}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0AAB
+A : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>맵</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> id
+B : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>포탈</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> id </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
   <si>
     <t>BOTH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CLIENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"FALSE"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -59,34 +123,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>map_path</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>width</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>height</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>start_point</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>teleport_points</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>monster_ids</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>respawn_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>map_type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -95,14 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"field"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>have_start_point</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>max_monster_count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -115,10 +147,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"xxxMap"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"초급 사냥터(Lv1~Lv10)"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -139,15 +167,69 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"points": [{"map_id": 101, "position": {"pos_x": 0, "pos_y": 0, "pos_z": 0}}, {"map_id": 102, "position": {"pos_x": 0, "pos_y": 0, "pos_z": 0}}, {"map_id": 103, "position": {"pos_x": 0, "pos_y": 0, "pos_z": 0}}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"points": [{"map_id": 100, "position": {"pos_x": 0, "pos_y": 0, "pos_z": 0}}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>template_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"hunting field"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>width_half_extent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>height_half_extent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>have_spawn_point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spawn_point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respawn_period</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summon_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"lists": [
+{"portal_id": 21, "type": "room", "src": {"pos_x": -7750, "pos_y": 10000, "pos_z": 0}, "dst": {"pos_x": -1000, "pos_y": 1000, "pos_z": 0}}
+]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"lists": [
+{"portal_id": 31, "type": "room", "src": {"pos_x": -7750, "pos_y": 0, "pos_z": 0}, "dst": {"pos_x": -1000, "pos_y": 0, "pos_z": 0}}
+]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"lists": [
+{"portal_id": 41, "type": "room", "src": {"pos_x": -7750, "pos_y": -10000, "pos_z": 0}, "dst": {"pos_x": -1000, "pos_y": -1000, "pos_z": 0}}
+]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"lists": [
+{"portal_id": 11, "type": "room", "src": {"pos_x": -1200, "pos_y": 1000, "pos_z": 0}, "dst": {"pos_x": -7750, "pos_y": 10000, "pos_z": 0}}, 
+{"portal_id": 12, "type": "room", "src": {"pos_x": -1200, "pos_y": 0, "pos_z": 0}, "dst": {"pos_x": -7750, "pos_y": 0, "pos_z": 0}}, 
+{"portal_id": 13, "type": "room", "src": {"pos_x": -1200, "pos_y": -1000, "pos_z": 0}, "dst": {"pos_x": -7750, "pos_y": -10000, "pos_z": 0}}
+]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -155,7 +237,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +252,21 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -194,9 +291,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,55 +611,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82845201-2628-4823-B6D1-8A4642A35A02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82845201-2628-4823-B6D1-8A4642A35A02}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="8" max="8" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
-      </c>
       <c r="L1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -573,178 +673,179 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1500</v>
+      </c>
+      <c r="F3">
+        <v>1500</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>2500</v>
+      </c>
+      <c r="F4">
+        <v>2500</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>20</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <v>100</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2500</v>
+      </c>
+      <c r="F5">
+        <v>2500</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2500</v>
+      </c>
+      <c r="F6">
+        <v>2500</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
         <v>3</v>
-      </c>
-      <c r="E3">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>101</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>50</v>
-      </c>
-      <c r="F4">
-        <v>50</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4">
-        <v>10</v>
-      </c>
-      <c r="K4">
-        <v>20</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>50</v>
-      </c>
-      <c r="F5">
-        <v>50</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>20</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>103</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
-      <c r="H6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA16F3D-8739-4637-8B88-7FCBD75E0057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC711A2-80D6-4150-8D3B-99CFE3CE0139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>BOTH</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,10 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>min_monster_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SERVER</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,40 +191,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>respawn_period</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>summon_count</t>
+    <t>[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>center_pos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pos_x" : -10000, "pos_y": 10000, "pos_z": 0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pos_x" : -10000, "pos_y": 0, "pos_z": 0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pos_x" : -10000, "pos_y": -10000, "pos_z": 0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster_respawn_time</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"lists": [
-{"portal_id": 21, "type": "room", "src": {"pos_x": -7750, "pos_y": 10000, "pos_z": 0}, "dst": {"pos_x": -1000, "pos_y": 1000, "pos_z": 0}}
+{"portal_id": 11, "type": "room", "src": {"pos_x": -1200, "pos_y": 1000, "pos_z": 0}, "dst": {"template_id": 20, "pos_x": -7750, "pos_y": 10000, "pos_z": 0}}, 
+{"portal_id": 12, "type": "room", "src": {"pos_x": -1200, "pos_y": 0, "pos_z": 0}, "dst": {"template_id": 30, "pos_x": -7750, "pos_y": 0, "pos_z": 0}}, 
+{"portal_id": 13, "type": "room", "src": {"pos_x": -1200, "pos_y": -1000, "pos_z": 0}, "dst": {"template_id": 40, "pos_x": -7750, "pos_y": -10000, "pos_z": 0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"lists": [
-{"portal_id": 31, "type": "room", "src": {"pos_x": -7750, "pos_y": 0, "pos_z": 0}, "dst": {"pos_x": -1000, "pos_y": 0, "pos_z": 0}}
+{"portal_id": 21, "type": "room", "src": {"pos_x": -7750, "pos_y": 10000, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": 1000, "pos_z": 0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"lists": [
-{"portal_id": 41, "type": "room", "src": {"pos_x": -7750, "pos_y": -10000, "pos_z": 0}, "dst": {"pos_x": -1000, "pos_y": -1000, "pos_z": 0}}
+{"portal_id": 31, "type": "room", "src": {"pos_x": -7750, "pos_y": 0, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": 0, "pos_z": 0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{"lists": [
-{"portal_id": 11, "type": "room", "src": {"pos_x": -1200, "pos_y": 1000, "pos_z": 0}, "dst": {"pos_x": -7750, "pos_y": 10000, "pos_z": 0}}, 
-{"portal_id": 12, "type": "room", "src": {"pos_x": -1200, "pos_y": 0, "pos_z": 0}, "dst": {"pos_x": -7750, "pos_y": 0, "pos_z": 0}}, 
-{"portal_id": 13, "type": "room", "src": {"pos_x": -1200, "pos_y": -1000, "pos_z": 0}, "dst": {"pos_x": -7750, "pos_y": -10000, "pos_z": 0}}
+{"portal_id": 41, "type": "room", "src": {"pos_x": -7750, "pos_y": -10000, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": -1000, "pos_z": 0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -612,15 +620,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82845201-2628-4823-B6D1-8A4642A35A02}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="8" max="8" width="13.59765625" customWidth="1"/>
+    <col min="9" max="9" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -629,37 +637,34 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
       <c r="L1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -673,34 +678,31 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>10</v>
       </c>
@@ -713,61 +715,61 @@
       <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>1500</v>
+      <c r="E3" t="s">
+        <v>16</v>
       </c>
       <c r="F3">
         <v>1500</v>
       </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="G3">
+        <v>1500</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>2500</v>
+      <c r="E4" t="s">
+        <v>26</v>
       </c>
       <c r="F4">
         <v>2500</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4">
+      <c r="G4">
+        <v>2500</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4">
         <v>20</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
       </c>
       <c r="L4">
         <v>10</v>
       </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>30</v>
       </c>
@@ -775,37 +777,34 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>2500</v>
+      <c r="E5" t="s">
+        <v>27</v>
       </c>
       <c r="F5">
         <v>2500</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5">
+      <c r="G5">
+        <v>2500</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5">
         <v>20</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
       </c>
       <c r="L5">
         <v>10</v>
       </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>40</v>
       </c>
@@ -813,34 +812,31 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>2500</v>
+      <c r="E6" t="s">
+        <v>28</v>
       </c>
       <c r="F6">
         <v>2500</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6">
+      <c r="G6">
+        <v>2500</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6">
         <v>20</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
       </c>
       <c r="L6">
         <v>10</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC711A2-80D6-4150-8D3B-99CFE3CE0139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBD42E2-2BD9-4A86-99AF-6A039627BB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -216,27 +216,27 @@
   </si>
   <si>
     <t>{"lists": [
-{"portal_id": 11, "type": "room", "src": {"pos_x": -1200, "pos_y": 1000, "pos_z": 0}, "dst": {"template_id": 20, "pos_x": -7750, "pos_y": 10000, "pos_z": 0}}, 
-{"portal_id": 12, "type": "room", "src": {"pos_x": -1200, "pos_y": 0, "pos_z": 0}, "dst": {"template_id": 30, "pos_x": -7750, "pos_y": 0, "pos_z": 0}}, 
-{"portal_id": 13, "type": "room", "src": {"pos_x": -1200, "pos_y": -1000, "pos_z": 0}, "dst": {"template_id": 40, "pos_x": -7750, "pos_y": -10000, "pos_z": 0}}
+{"portal_id": 21, "type": "room", "src": {"pos_x": -7750, "pos_y": 10000, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": 1000, "pos_z": 0, "yaw":0.0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"lists": [
-{"portal_id": 21, "type": "room", "src": {"pos_x": -7750, "pos_y": 10000, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": 1000, "pos_z": 0}}
+{"portal_id": 31, "type": "room", "src": {"pos_x": -7750, "pos_y": 0, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": 0, "pos_z": 0, "yaw":0.0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"lists": [
-{"portal_id": 31, "type": "room", "src": {"pos_x": -7750, "pos_y": 0, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": 0, "pos_z": 0}}
+{"portal_id": 41, "type": "room", "src": {"pos_x": -7750, "pos_y": -10000, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": -1000, "pos_z": 0, "yaw":0.0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{"lists": [
-{"portal_id": 41, "type": "room", "src": {"pos_x": -7750, "pos_y": -10000, "pos_z": 0}, "dst": {"template_id": 10, "pos_x": -1000, "pos_y": -1000, "pos_z": 0}}
+{"portal_id": 11, "type": "room", "src": {"pos_x": -1200, "pos_y": 1000, "pos_z": 0}, "dst": {"template_id": 20, "pos_x": -8000, "pos_y": 10000, "pos_z": 0, "yaw":180.0}}, 
+{"portal_id": 12, "type": "room", "src": {"pos_x": -1200, "pos_y": 0, "pos_z": 0}, "dst": {"template_id": 30, "pos_x": -8000, "pos_y": 0, "pos_z": 0, "yaw":180.0}}, 
+{"portal_id": 13, "type": "room", "src": {"pos_x": -1200, "pos_y": -1000, "pos_z": 0}, "dst": {"template_id": 40, "pos_x": -8000, "pos_y": -10000, "pos_z": 0, "yaw":180.0}}
 ]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -728,7 +728,7 @@
         <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
         <v>24</v>
@@ -757,7 +757,7 @@
         <v>2500</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
@@ -792,7 +792,7 @@
         <v>2500</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
         <v>14</v>
@@ -827,7 +827,7 @@
         <v>2500</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>

--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBD42E2-2BD9-4A86-99AF-6A039627BB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9307465-93BA-4C99-B816-B840E8565FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="5520" yWindow="1656" windowWidth="23040" windowHeight="12204" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="맵&amp;포탈(000~999)" sheetId="3" r:id="rId1"/>
@@ -115,14 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"중급 사냥터(Lv11~Lv30)"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"고급 사냥터(Lv31~Lv50)"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>monster_ids</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -140,10 +132,6 @@
   </si>
   <si>
     <t>SERVER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"초급 사냥터(Lv1~Lv10)"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -238,6 +226,18 @@
 {"portal_id": 12, "type": "room", "src": {"pos_x": -1200, "pos_y": 0, "pos_z": 0}, "dst": {"template_id": 30, "pos_x": -8000, "pos_y": 0, "pos_z": 0, "yaw":180.0}}, 
 {"portal_id": 13, "type": "room", "src": {"pos_x": -1200, "pos_y": -1000, "pos_z": 0}, "dst": {"template_id": 40, "pos_x": -8000, "pos_y": -10000, "pos_z": 0, "yaw":180.0}}
 ]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"초급 사냥터"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"중급 사냥터"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"고급 사냥터"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -628,40 +628,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
       <c r="L1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -678,28 +678,28 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -710,13 +710,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>1500</v>
@@ -725,13 +725,13 @@
         <v>1500</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -739,16 +739,16 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>2500</v>
@@ -757,10 +757,10 @@
         <v>2500</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>20</v>
@@ -774,16 +774,16 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>2500</v>
@@ -792,10 +792,10 @@
         <v>2500</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K5">
         <v>20</v>
@@ -809,16 +809,16 @@
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>2500</v>
@@ -827,10 +827,10 @@
         <v>2500</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>20</v>

--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9307465-93BA-4C99-B816-B840E8565FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B327916-54BA-4E94-8CE5-1D69CE0068CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="1656" windowWidth="23040" windowHeight="12204" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="맵&amp;포탈(000~999)" sheetId="3" r:id="rId1"/>

--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B327916-54BA-4E94-8CE5-1D69CE0068CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407F689A-B08C-408F-80E9-D5E6685DB1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="24" yWindow="1872" windowWidth="24828" windowHeight="12204" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="맵&amp;포탈(000~999)" sheetId="3" r:id="rId1"/>
@@ -763,7 +763,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -798,7 +798,7 @@
         <v>11</v>
       </c>
       <c r="K5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -833,7 +833,7 @@
         <v>12</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>10</v>

--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407F689A-B08C-408F-80E9-D5E6685DB1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48980E9-50C1-4B5A-AB08-5B9008565054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="1872" windowWidth="24828" windowHeight="12204" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="맵&amp;포탈(000~999)" sheetId="3" r:id="rId1"/>
@@ -167,14 +167,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>have_spawn_point</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spawn_point</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>portals</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -238,6 +230,14 @@
   </si>
   <si>
     <t>"고급 사냥터"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>have_return_point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>return_point</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -637,10 +637,10 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
@@ -649,10 +649,10 @@
         <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>8</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -728,10 +728,10 @@
         <v>13</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -739,7 +739,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>2500</v>
@@ -757,7 +757,7 @@
         <v>2500</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
         <v>10</v>
@@ -774,7 +774,7 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -783,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>2500</v>
@@ -792,7 +792,7 @@
         <v>2500</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
         <v>11</v>
@@ -809,7 +809,7 @@
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>2500</v>
@@ -827,7 +827,7 @@
         <v>2500</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J6" t="s">
         <v>12</v>

--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48980E9-50C1-4B5A-AB08-5B9008565054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F69167-C4B8-417D-871D-CE93A14624C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="4116" yWindow="2028" windowWidth="24828" windowHeight="12204" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="맵&amp;포탈(000~999)" sheetId="3" r:id="rId1"/>
@@ -233,11 +233,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>have_return_point</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>return_point</t>
+    <t>respawn_point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>has_respawn_point</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -637,7 +637,7 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
         <v>20</v>
@@ -649,7 +649,7 @@
         <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I1" t="s">
         <v>18</v>

--- a/Server/Common/GameDatasheet/Original_Map.xlsx
+++ b/Server/Common/GameDatasheet/Original_Map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F69167-C4B8-417D-871D-CE93A14624C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1A9908-E161-4EFB-95CA-C0C45D555F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4116" yWindow="2028" windowWidth="24828" windowHeight="12204" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>BOTH</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -238,6 +238,10 @@
   </si>
   <si>
     <t>has_respawn_point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -620,51 +624,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82845201-2628-4823-B6D1-8A4642A35A02}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="9" max="9" width="13.59765625" customWidth="1"/>
+    <col min="10" max="10" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>32</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -678,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -701,147 +708,163 @@
       <c r="L2" t="s">
         <v>9</v>
       </c>
+      <c r="M2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>1111</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
-      </c>
-      <c r="F3">
-        <v>1500</v>
       </c>
       <c r="G3">
         <v>1500</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3">
+        <v>1500</v>
+      </c>
+      <c r="I3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>1111</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>21</v>
-      </c>
-      <c r="F4">
-        <v>2500</v>
       </c>
       <c r="G4">
         <v>2500</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="H4">
+        <v>2500</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4">
+      <c r="K4" t="s">
         <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
       </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>1111</v>
+      </c>
+      <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>22</v>
-      </c>
-      <c r="F5">
-        <v>2500</v>
       </c>
       <c r="G5">
         <v>2500</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="H5">
+        <v>2500</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>11</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
       </c>
+      <c r="M5">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>40</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>1111</v>
+      </c>
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6">
-        <v>2500</v>
       </c>
       <c r="G6">
         <v>2500</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="H6">
+        <v>2500</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>12</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>